--- a/qualitative analysis/Coding_scheme.xlsx
+++ b/qualitative analysis/Coding_scheme.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tuenl-my.sharepoint.com/personal/s_rasti_tue_nl/Documents/Sajedeh PhD Project/Study 2/Quantitative - openAlex/Large_team_openalex_coordination/qualitative analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_F25DC773A252ABDACC1048A8E95B678A5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4AE408F-D4F2-438E-8619-54F616FEA7C2}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_F25DC773A252ABDACC1048A8E95B678A5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9346A08-8297-453B-A8EA-7FA386EDDD99}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -106,10 +105,6 @@
   </si>
   <si>
     <t>Papers with the main aim of showing strong non-evidential support for a position or perspective</t>
-  </si>
-  <si>
-    <t>if RCT does not have multiple data collection time points
-long study period (e.g., data was collected between 2015 and 2020)</t>
   </si>
   <si>
     <t>Intensive data collection (this can be due to expensive tools such as fMRI or genetic study, neural studies, ... or due to hard-to-reach samples (e.g., primates, mental conditions, comorbid conditions)) [if there is an indication of general population, it does not count as intensive data collection] - collecting more data than needed (ideally in the presence of a-priory power analysis) - Collecting a lot of data (for quantitative studies it is defined as &gt;1000 for online data collection and &gt;200 for in-person)</t>
@@ -215,6 +210,11 @@
     <t>multiple data collection time points (multiple months or years), randomized controlled trials with follow-ups, longitudinal studies and cohorts
 multi-stage consensus development
 development and testing an instrument in one paper (or performing a study and the replication in the same paper)</t>
+  </si>
+  <si>
+    <t>if RCT does not have multiple data collection time points
+long study period (e.g., data was collected between 2015 and 2020)
+the multiple time collections are less than 3 months</t>
   </si>
 </sst>
 </file>
@@ -703,7 +703,7 @@
         <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="87" x14ac:dyDescent="0.35">
@@ -714,7 +714,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87" x14ac:dyDescent="0.35">
@@ -725,13 +725,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="174" x14ac:dyDescent="0.35">
@@ -742,10 +742,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -759,10 +759,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="203" x14ac:dyDescent="0.35">
@@ -773,10 +773,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="116" x14ac:dyDescent="0.35">
@@ -787,15 +787,15 @@
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="217.5" x14ac:dyDescent="0.35">
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
